--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-emed-operationoutcome-details.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
